--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484809_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484809_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5157</v>
+        <v>5.3296</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0988</v>
+        <v>3.8598</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4169</v>
+        <v>1.4698</v>
       </c>
       <c r="G2" t="n">
         <v>4.6183</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5555</v>
+        <v>0.2584</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0582</v>
+        <v>-0.2972</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5027</v>
+        <v>0.5556</v>
       </c>
       <c r="V2" t="n">
         <v>0.6415999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4771</v>
+        <v>3.4708</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4733</v>
+        <v>2.4935</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0038</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.8257</v>
@@ -688,13 +688,13 @@
         <v>2.0757</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4062</v>
+        <v>0.3999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0152</v>
+        <v>0.0354</v>
       </c>
       <c r="U3" t="n">
-        <v>0.391</v>
+        <v>0.3645</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8166</v>
+        <v>1.8211</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7323</v>
+        <v>2.3928</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9158</v>
+        <v>-0.5717</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0172</v>
+        <v>1.7268</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5672</v>
+        <v>0.677</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.5501</v>
+        <v>1.0498</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7194</v>
+        <v>3.4819</v>
       </c>
       <c r="K4" t="n">
-        <v>5.0399</v>
+        <v>1.458</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3205</v>
+        <v>2.0239</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7022</v>
+        <v>-1.7551</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4727</v>
+        <v>-0.781</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2295</v>
+        <v>-0.9741</v>
       </c>
       <c r="P4" t="n">
         <v>-0.1887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6983</v>
+        <v>0.7548</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2333</v>
+        <v>0.283</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8999</v>
+        <v>-0.1455</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3334</v>
+        <v>0.4286</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>J. IBAÑEZ TEJERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5733</v>
+        <v>1.5509</v>
       </c>
       <c r="E5" t="n">
-        <v>2.198</v>
+        <v>1.5509</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6246</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7268</v>
+        <v>1.5509</v>
       </c>
       <c r="H5" t="n">
-        <v>0.677</v>
+        <v>0.317</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0498</v>
+        <v>1.2339</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4819</v>
+        <v>1.5509</v>
       </c>
       <c r="K5" t="n">
-        <v>1.458</v>
+        <v>0.317</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0239</v>
+        <v>1.2339</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7551</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.781</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9741</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0353</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3404</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3757</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. IBAÑEZ TEJERO</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5509</v>
+        <v>1.4146</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5509</v>
+        <v>3.3039</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-1.8893</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5509</v>
+        <v>2.0172</v>
       </c>
       <c r="H6" t="n">
-        <v>0.317</v>
+        <v>4.5672</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2339</v>
+        <v>-2.5501</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5509</v>
+        <v>4.7194</v>
       </c>
       <c r="K6" t="n">
-        <v>0.317</v>
+        <v>5.0399</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2339</v>
+        <v>-0.3205</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-2.7022</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.4727</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-2.2295</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.8314</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4716</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.3598</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>J. IBANEZ TEJERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.366</v>
+        <v>0.9681</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4628</v>
+        <v>3.2643</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9033</v>
+        <v>-2.2962</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1102</v>
+        <v>2.2949</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7513</v>
+        <v>1.3946</v>
       </c>
       <c r="I7" t="n">
-        <v>0.641</v>
+        <v>0.9003</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2756</v>
+        <v>4.2834</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1111</v>
+        <v>2.1928</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1645</v>
+        <v>2.0906</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3859</v>
+        <v>-1.9885</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.7982</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4765</v>
+        <v>-1.1902</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9435</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9435</v>
+        <v>2.2644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8536</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1147</v>
+        <v>-0.0374</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9683</v>
+        <v>0.5409</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3208</v>
+        <v>-1.2642</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3018</v>
+        <v>1.8488</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6226</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. IBANEZ TEJERO</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3558</v>
+        <v>0.8474</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7314</v>
+        <v>0.288</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3755</v>
+        <v>0.5594</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2949</v>
+        <v>-0.1102</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3946</v>
+        <v>-0.7513</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9003</v>
+        <v>0.641</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2834</v>
+        <v>0.2756</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1928</v>
+        <v>0.1111</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0906</v>
+        <v>0.1645</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9885</v>
+        <v>-0.3859</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7982</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1902</v>
+        <v>0.4765</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2644</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8912</v>
+        <v>0.3349</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4296</v>
+        <v>-0.2894</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4615</v>
+        <v>0.6243</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2642</v>
+        <v>-0.3208</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8488</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.113</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0912</v>
+        <v>0.6038</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3388</v>
+        <v>0.6899</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.43</v>
+        <v>-0.0861</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8547</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3122</v>
+        <v>0.3828</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5168</v>
+        <v>-0.1657</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2046</v>
+        <v>0.5485</v>
       </c>
       <c r="V10" t="n">
         <v>0.3208</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1024</v>
+        <v>0.1513</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.7683</v>
       </c>
       <c r="F11" t="n">
         <v>-0.617</v>
@@ -1312,10 +1312,10 @@
         <v>0.1887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0588</v>
+        <v>0.3124</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2352</v>
+        <v>0.0185</v>
       </c>
       <c r="U11" t="n">
         <v>0.2939</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1662</v>
+        <v>0.0106</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1064</v>
+        <v>0.2038</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2726</v>
+        <v>-0.1933</v>
       </c>
       <c r="G12" t="n">
         <v>0.2047</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3709</v>
+        <v>-0.1941</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2939</v>
+        <v>-0.1965</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.077</v>
+        <v>0.0024</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8676</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1537</v>
+        <v>-0.8799</v>
       </c>
       <c r="F13" t="n">
-        <v>0.286</v>
+        <v>0.0215</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3699</v>
@@ -1468,13 +1468,13 @@
         <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>0.823</v>
+        <v>0.8323</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3498</v>
+        <v>-0.076</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1729</v>
+        <v>0.9083</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3208</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.0619</v>
+        <v>15.9437</v>
       </c>
       <c r="E14" t="n">
-        <v>17.6875</v>
+        <v>18.56920000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6255</v>
+        <v>-2.625599999999999</v>
       </c>
       <c r="G14" t="n">
         <v>13.886</v>
@@ -1537,7 +1537,7 @@
         <v>-8.115600000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9435</v>
+        <v>-0.9435000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.1525</v>
@@ -1546,16 +1546,16 @@
         <v>13.209</v>
       </c>
       <c r="S14" t="n">
-        <v>3.062800000000001</v>
+        <v>3.9445</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5643</v>
+        <v>-0.6821999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>4.627000000000001</v>
+        <v>4.6268</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9434</v>
+        <v>-0.9434000000000005</v>
       </c>
       <c r="W14" t="n">
         <v>4.3202</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>H. RODRÍGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6894</v>
+        <v>1.2339</v>
       </c>
       <c r="E16" t="n">
-        <v>0.541</v>
+        <v>1.2339</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1484</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1805</v>
+        <v>1.2339</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7929</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6124000000000001</v>
+        <v>1.2339</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2262</v>
+        <v>1.2339</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1028</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1234</v>
+        <v>1.2339</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0457</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3099</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7358</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3203</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7112000000000001</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6091</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. RODRÍGUEZ GUTIERREZ</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2339</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2339</v>
+        <v>-0.0436</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.9897</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2339</v>
+        <v>1.1805</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.7929</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2339</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2339</v>
+        <v>2.2262</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2.1028</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2339</v>
+        <v>0.1234</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.0457</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.3099</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.7358</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.1266</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.4503</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0985</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.839</v>
+        <v>1.5467</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.6611</v>
       </c>
       <c r="G18" t="n">
         <v>0.5601</v>
@@ -1858,13 +1858,13 @@
         <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0277</v>
+        <v>-0.2406</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1793</v>
+        <v>-0.113</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2069</v>
+        <v>-0.1276</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3451</v>
+        <v>-0.2657</v>
       </c>
       <c r="E21" t="n">
         <v>-0.7425</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3974</v>
+        <v>0.4768</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4691</v>
@@ -2092,13 +2092,13 @@
         <v>0.1887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.0147</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1117</v>
+        <v>0.1911</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CARR</t>
+          <t>R. DIAZ GALIAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4176</v>
+        <v>-1.2967</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0751</v>
+        <v>-0.9124</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4927</v>
+        <v>-0.3843</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3635</v>
+        <v>-2.8063</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8358</v>
+        <v>-0.9986</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1993</v>
+        <v>-1.8077</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0091</v>
+        <v>-0.2712</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5029</v>
+        <v>0.2379</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5062</v>
+        <v>-0.5091</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.3726</v>
+        <v>-2.5351</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.6671</v>
+        <v>-1.2365</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.7055</v>
+        <v>-1.2986</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3209</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9627</v>
+        <v>-2.0757</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6418</v>
+        <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3368</v>
+        <v>-0.1129</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.4333</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4833</v>
+        <v>0.3204</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6036</v>
+        <v>2.1886</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8488</v>
+        <v>1.8678</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2452</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. DIAZ GALIAN</t>
+          <t>J. CARR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5277</v>
+        <v>-1.4729</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3022</v>
+        <v>2.0751</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2255</v>
+        <v>-3.548</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8063</v>
+        <v>-0.3635</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9986</v>
+        <v>0.8358</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8077</v>
+        <v>-1.1993</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2712</v>
+        <v>5.0091</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2379</v>
+        <v>3.5029</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5091</v>
+        <v>1.5062</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5351</v>
+        <v>-5.3726</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2365</v>
+        <v>-2.6671</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2986</v>
+        <v>-2.7055</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5661</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0757</v>
+        <v>-3.9627</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5096</v>
+        <v>2.6418</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3439</v>
+        <v>-0.3921</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.823</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4792</v>
+        <v>0.428</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1886</v>
+        <v>0.6036</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8678</v>
+        <v>1.8488</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3208</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2649</v>
+        <v>-1.9679</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2754</v>
+        <v>1.178</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5403</v>
+        <v>-3.1459</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3142</v>
@@ -2326,13 +2326,13 @@
         <v>1.6983</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5168</v>
+        <v>-0.2197</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.585</v>
+        <v>-0.6824</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0682</v>
+        <v>0.4627</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2452</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4738</v>
+        <v>-3.3439</v>
       </c>
       <c r="E25" t="n">
         <v>-1.3721</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1017</v>
+        <v>-1.9718</v>
       </c>
       <c r="G25" t="n">
         <v>-3.3562</v>
@@ -2404,13 +2404,13 @@
         <v>0.1887</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3063</v>
+        <v>-0.1764</v>
       </c>
       <c r="T25" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1299</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.9085</v>
+        <v>-3.4167</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0669</v>
+        <v>0.1644</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.9755</v>
+        <v>-3.581</v>
       </c>
       <c r="G26" t="n">
         <v>-5.7048</v>
@@ -2482,13 +2482,13 @@
         <v>2.6418</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9776</v>
+        <v>-0.4857</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8789</v>
+        <v>-0.7815</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0987</v>
+        <v>0.2958</v>
       </c>
       <c r="V26" t="n">
         <v>0.3208</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.015</v>
+        <v>-4.5831</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8952</v>
+        <v>-0.408</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.1199</v>
+        <v>-4.1751</v>
       </c>
       <c r="G28" t="n">
         <v>-3.8227</v>
@@ -2638,13 +2638,13 @@
         <v>2.2644</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.0793</v>
+        <v>-0.6474</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.4697</v>
+        <v>-0.9825</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3904</v>
+        <v>0.3351</v>
       </c>
       <c r="V28" t="n">
         <v>-1.2452</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-15.0617</v>
+        <v>-14.4122</v>
       </c>
       <c r="E29" t="n">
-        <v>2.625700000000001</v>
+        <v>2.6259</v>
       </c>
       <c r="F29" t="n">
-        <v>-17.6875</v>
+        <v>-17.038</v>
       </c>
       <c r="G29" t="n">
         <v>-13.8857</v>
@@ -2686,7 +2686,7 @@
         <v>-7.0669</v>
       </c>
       <c r="I29" t="n">
-        <v>-6.818800000000001</v>
+        <v>-6.8188</v>
       </c>
       <c r="J29" t="n">
         <v>15.1979</v>
@@ -2716,13 +2716,13 @@
         <v>14.1525</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.0629</v>
+        <v>-2.4132</v>
       </c>
       <c r="T29" t="n">
-        <v>-4.626899999999999</v>
+        <v>-4.6269</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5642</v>
+        <v>2.2136</v>
       </c>
       <c r="V29" t="n">
         <v>0.9434</v>
